--- a/backend/Item PLU Ranges.xlsx
+++ b/backend/Item PLU Ranges.xlsx
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C231" s="8" t="n">
-        <v>4007400</v>
+        <v>4007300</v>
       </c>
       <c r="D231" s="8" t="n">
         <v>4007399</v>
@@ -6934,326 +6934,326 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
+      <c r="A360" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B360" s="0" t="inlineStr">
         <is>
           <t>Full Sandwich Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C360" t="n">
+      <c r="C360" s="0" t="n">
         <v>40060000</v>
       </c>
-      <c r="D360" t="n">
+      <c r="D360" s="0" t="n">
         <v>40060099</v>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
+      <c r="A361" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B361" s="0" t="inlineStr">
         <is>
           <t>Full Salad Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C361" t="n">
+      <c r="C361" s="0" t="n">
         <v>40060100</v>
       </c>
-      <c r="D361" t="n">
+      <c r="D361" s="0" t="n">
         <v>40060199</v>
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
+      <c r="A362" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B362" s="0" t="inlineStr">
         <is>
           <t>Full Pizza Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C362" t="n">
+      <c r="C362" s="0" t="n">
         <v>40060200</v>
       </c>
-      <c r="D362" t="n">
+      <c r="D362" s="0" t="n">
         <v>40060299</v>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
+      <c r="A363" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B363" s="0" t="inlineStr">
         <is>
           <t>Bowl Soup Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C363" t="n">
+      <c r="C363" s="0" t="n">
         <v>40060300</v>
       </c>
-      <c r="D363" t="n">
+      <c r="D363" s="0" t="n">
         <v>40060399</v>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
+      <c r="A364" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B364" s="0" t="inlineStr">
         <is>
           <t>Full Mac Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C364" t="n">
+      <c r="C364" s="0" t="n">
         <v>40060500</v>
       </c>
-      <c r="D364" t="n">
+      <c r="D364" s="0" t="n">
         <v>40060599</v>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
+      <c r="A365" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B365" s="0" t="inlineStr">
         <is>
           <t>Half Sandwich Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C365" t="n">
+      <c r="C365" s="0" t="n">
         <v>40060600</v>
       </c>
-      <c r="D365" t="n">
+      <c r="D365" s="0" t="n">
         <v>40060699</v>
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
+      <c r="A366" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B366" s="0" t="inlineStr">
         <is>
           <t>Half Salad Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C366" t="n">
+      <c r="C366" s="0" t="n">
         <v>40060700</v>
       </c>
-      <c r="D366" t="n">
+      <c r="D366" s="0" t="n">
         <v>40060799</v>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
+      <c r="A367" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B367" s="0" t="inlineStr">
         <is>
           <t>Cup Soup Pairing (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C367" t="n">
+      <c r="C367" s="0" t="n">
         <v>40060800</v>
       </c>
-      <c r="D367" t="n">
+      <c r="D367" s="0" t="n">
         <v>40060899</v>
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
+      <c r="A368" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B368" s="0" t="inlineStr">
         <is>
           <t>Pick 3 Half Sandwich (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C368" t="n">
+      <c r="C368" s="0" t="n">
         <v>40060900</v>
       </c>
-      <c r="D368" t="n">
+      <c r="D368" s="0" t="n">
         <v>40060999</v>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
+      <c r="A369" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B369" s="0" t="inlineStr">
         <is>
           <t>Pick 3 Half Salad (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C369" t="n">
+      <c r="C369" s="0" t="n">
         <v>40061000</v>
       </c>
-      <c r="D369" t="n">
+      <c r="D369" s="0" t="n">
         <v>40061099</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
+      <c r="A370" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B370" s="0" t="inlineStr">
         <is>
           <t>Pick 3 Cup Soup (POS Entree) (OLO)</t>
         </is>
       </c>
-      <c r="C370" t="n">
+      <c r="C370" s="0" t="n">
         <v>40061100</v>
       </c>
-      <c r="D370" t="n">
+      <c r="D370" s="0" t="n">
         <v>40061199</v>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
+      <c r="A371" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B371" s="0" t="inlineStr">
         <is>
           <t>Full Sandwich Pairing (Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C371" t="n">
+      <c r="C371" s="0" t="n">
         <v>40070000</v>
       </c>
-      <c r="D371" t="n">
+      <c r="D371" s="0" t="n">
         <v>40070099</v>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
+      <c r="A372" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B372" s="0" t="inlineStr">
         <is>
           <t>Full Salad Pairing (Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C372" t="n">
+      <c r="C372" s="0" t="n">
         <v>40070100</v>
       </c>
-      <c r="D372" t="n">
+      <c r="D372" s="0" t="n">
         <v>40070199</v>
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
+      <c r="A373" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B373" s="0" t="inlineStr">
         <is>
           <t>Full Pizza Pairing (Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C373" t="n">
+      <c r="C373" s="0" t="n">
         <v>40070200</v>
       </c>
-      <c r="D373" t="n">
+      <c r="D373" s="0" t="n">
         <v>40070299</v>
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
+      <c r="A374" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B374" s="0" t="inlineStr">
         <is>
           <t>Soup Pairing (Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C374" t="n">
+      <c r="C374" s="0" t="n">
         <v>40070300</v>
       </c>
-      <c r="D374" t="n">
+      <c r="D374" s="0" t="n">
         <v>40070399</v>
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
+      <c r="A375" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B375" s="0" t="inlineStr">
         <is>
           <t>Half Salad Pairing (Pick 3 Add on Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C375" t="n">
+      <c r="C375" s="0" t="n">
         <v>40071000</v>
       </c>
-      <c r="D375" t="n">
+      <c r="D375" s="0" t="n">
         <v>40071099</v>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
+      <c r="A376" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B376" s="0" t="inlineStr">
         <is>
           <t>Cup Soup Pairing (Pick 3 Add on Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C376" t="n">
+      <c r="C376" s="0" t="n">
         <v>40071100</v>
       </c>
-      <c r="D376" t="n">
+      <c r="D376" s="0" t="n">
         <v>40071199</v>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
+      <c r="A377" s="0" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="B377" s="0" t="inlineStr">
         <is>
           <t>Premium Side Pairing (Pick 3 Add on Modifier Choice) (OLO)</t>
         </is>
       </c>
-      <c r="C377" t="n">
+      <c r="C377" s="0" t="n">
         <v>40071200</v>
       </c>
-      <c r="D377" t="n">
+      <c r="D377" s="0" t="n">
         <v>40071299</v>
       </c>
     </row>
